--- a/plantillas/Plantilla_Reporte_Mensual_Cuentas_Criticas.xlsx
+++ b/plantillas/Plantilla_Reporte_Mensual_Cuentas_Criticas.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B20"/>
+  <dimension ref="B2:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -542,80 +542,122 @@
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>3. Indique el 'Periodo_Reporte' en formato AAAA-MM. El ciclo de seguimiento va de Septiembre a Julio (ej. 2026-09 a 2027-07); no se reportan cuentas en Agosto.</t>
+          <t>3. 'Codigo_Familia' es OPCIONAL pero funcional: si coincide con una familia ya existente en el sistema,</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>4. 'Balance_Anio_Anterior': si la familia arrastra una deuda de un año escolar previo, colóquela aquí. Este monto se suma al balance del año en curso.</t>
+          <t xml:space="preserve">   el estudiante se vinculará automáticamente a esa familia al importar (no hace falta ningún paso aparte).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>5. 'Balance_Meses_Actuales': deuda acumulada solo de los meses del año escolar en curso que están sin pagar (no incluya aquí el balance de años anteriores).</t>
+          <t xml:space="preserve">   Si el código no existe todavía, esa fila se importa igual pero el vínculo de familia no se actualiza.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>6. Los abonos (pagos parciales) NO se registran en esta plantilla — se registran directamente dentro de la aplicación, con su fecha, y el sistema calcula el balance pendiente actual automáticamente.</t>
+          <t>4. 'Nombre_Estudiante', 'Nombre_Familia', 'Nivel' y 'Grado' son solo informativos (para que reconozca cada</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>7. Cada importación crea un nuevo snapshot histórico de ese periodo — no borra ni sobrescribe meses anteriores.</t>
+          <t xml:space="preserve">   fila al editar en Excel) — no se usan para actualizar esos datos, se ignoran al importar.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>8. Las columnas con encabezado en fondo azul oscuro son obligatorias (Balance_Anio_Anterior es opcional, déjela en 0 si no aplica).</t>
+          <t>5. Indique el 'Periodo_Reporte' en formato AAAA-MM. El ciclo de seguimiento va de Septiembre a Julio.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>9. Elimine las filas de ejemplo (en gris) antes de subir el archivo.</t>
+          <t>6. 'Balance_Anio_Anterior': deuda de un año escolar previo. 'Balance_Meses_Actuales': deuda del año en curso.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>7. Los abonos (pagos parciales) NO se registran aquí — se registran dentro de la aplicación, con su fecha.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Notas importantes:</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>8. Cada importación crea un nuevo snapshot histórico de ese periodo — no borra ni sobrescribe meses anteriores.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>• El semáforo de mora lo calcula el sistema automáticamente según 'Meses_Adeudados' (meses del año escolar en curso).</t>
+          <t>9. Las columnas con encabezado en fondo azul oscuro son obligatorias.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>10. Elimine las filas de ejemplo (en gris) antes de subir el archivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Notas importantes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>• El semáforo de mora lo calcula el sistema automáticamente según 'Meses_Adeudados'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
           <t>• Los montos deben ser números, sin símbolo de moneda ni separadores de miles (ej. 45000.00).</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>• Las fechas deben tener formato AAAA-MM-DD (ej. 2026-09-15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>• Este mismo formato es el que genera el botón "Exportar (reimportable)" del Reporte Mensual dentro</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  de la app — puede exportar, editar en Excel, y volver a subir el mismo archivo directamente.</t>
         </is>
       </c>
     </row>
@@ -630,21 +672,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -653,57 +700,82 @@
           <t>Codigo_Estudiante*</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Nombre_Estudiante</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Codigo_Familia</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Nombre_Familia</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Nivel</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Grado</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Periodo_Reporte(AAAA-MM)*</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Meses_Adeudados*</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Balance_Anio_Anterior</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Balance_Meses_Actuales*</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Fecha_Ultimo_Pago</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Monto_Ultimo_Pago</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>Estado_Gestion*</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>Responsable_Asignado*</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Fecha_Ultima_Gestion</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Proximo_Seguimiento</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -717,41 +789,66 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
+          <t>María Rodríguez Pérez</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>FAM-0001</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Juana Pérez de Rodríguez</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Nivel Primario</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>3er Grado A</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="H2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="I2" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J2" s="7" t="n">
         <v>8000</v>
       </c>
-      <c r="E2" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F2" s="7" t="inlineStr"/>
-      <c r="G2" s="7" t="inlineStr"/>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr"/>
+      <c r="L2" s="7" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>Contactado</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Ana Gómez</t>
         </is>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Arrastra deuda del año escolar anterior.</t>
         </is>
@@ -765,37 +862,62 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
+          <t>Luis Mateo Fernández</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>FAM-0002</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Mateo</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Nivel Secundario</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>1er Año B</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="H3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="I3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="J3" s="7" t="n">
         <v>8000</v>
       </c>
-      <c r="F3" s="7" t="inlineStr"/>
-      <c r="G3" s="7" t="inlineStr"/>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr"/>
+      <c r="L3" s="7" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>Sin respuesta</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Ana Gómez</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr"/>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr"/>
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t>No contesta llamadas.</t>
         </is>
@@ -803,7 +925,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Seleccione un estado de gestión válido" type="list">
+    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Seleccione un estado de gestión válido" type="list">
       <formula1>"Pendiente,Contactado,Compromiso de pago,Pago parcial,Regularizado,Sin respuesta"</formula1>
     </dataValidation>
   </dataValidations>
